--- a/backend/data/financials_by_company/0026.HK.xlsx
+++ b/backend/data/financials_by_company/0026.HK.xlsx
@@ -3148,187 +3148,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3431,28 +3431,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>57.15</v>
+        <v>57.1</v>
       </c>
       <c r="V2" t="n">
-        <v>57.2</v>
+        <v>58</v>
       </c>
       <c r="W2" t="n">
-        <v>57.15</v>
+        <v>58</v>
       </c>
       <c r="X2" t="n">
-        <v>57.4</v>
+        <v>58</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.15</v>
+        <v>57.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>57.2</v>
+        <v>58</v>
       </c>
       <c r="AA2" t="n">
-        <v>57.15</v>
+        <v>58</v>
       </c>
       <c r="AB2" t="n">
-        <v>57.4</v>
+        <v>58</v>
       </c>
       <c r="AC2" t="n">
         <v>0.6</v>
@@ -3467,31 +3467,31 @@
         <v>0.3125</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.277</v>
+        <v>0.281</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>6200</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>6200</v>
       </c>
       <c r="AK2" t="n">
-        <v>4258</v>
+        <v>4105</v>
       </c>
       <c r="AL2" t="n">
-        <v>2872</v>
+        <v>3340</v>
       </c>
       <c r="AM2" t="n">
-        <v>2872</v>
+        <v>3340</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.9</v>
+        <v>57.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>58.55</v>
+        <v>58</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -3500,13 +3500,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2595562496</v>
+        <v>2622693632</v>
       </c>
       <c r="AS2" t="n">
-        <v>2584257620</v>
+        <v>2600084220</v>
       </c>
       <c r="AT2" t="n">
-        <v>52.1</v>
+        <v>53.75</v>
       </c>
       <c r="AU2" t="n">
         <v>62</v>
@@ -3518,19 +3518,19 @@
         <v>23.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.753992</v>
+        <v>17.939571</v>
       </c>
       <c r="AY2" t="n">
-        <v>57.826</v>
+        <v>57.823</v>
       </c>
       <c r="AZ2" t="n">
-        <v>58.7325</v>
+        <v>58.61075</v>
       </c>
       <c r="BA2" t="n">
         <v>0.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.008748906000000001</v>
+        <v>0.008756567999999999</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1287410304</v>
+        <v>1314541696</v>
       </c>
       <c r="BF2" t="n">
         <v>-1.4686</v>
@@ -3565,7 +3565,7 @@
         <v>146.383</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.39212206</v>
+        <v>0.3962209</v>
       </c>
       <c r="BN2" t="n">
         <v>1751241600</v>
@@ -3583,16 +3583,16 @@
         <v>-4.74</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.805999999999999</v>
+        <v>8.992000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>11.841</v>
+        <v>12.09</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.07830191</v>
+        <v>0.05253458</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BW2" t="n">
         <v>1.1</v>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>57.4</v>
+        <v>58</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -3704,138 +3704,138 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>CHINA MOTOR BUS</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>1783062242</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.5761849</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>58</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.9000015</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>58.0 - 58.0</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>4258</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>5.300003</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0.10172751</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>52.1 - 62.0</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>-4.5999985</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.07419352</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>7.8301907</v>
-      </c>
-      <c r="DI2" t="n">
+      <c r="DL2" t="n">
+        <v>4105</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.07906977</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>53.75 - 62.0</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.06451613</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>5.253458</v>
+      </c>
+      <c r="DS2" t="n">
         <v>1740651475</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DT2" t="n">
         <v>1740651475</v>
       </c>
-      <c r="DK2" t="b">
+      <c r="DU2" t="b">
         <v>0</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="DV2" t="n">
         <v>-4.74</v>
       </c>
-      <c r="DM2" t="n">
-        <v>-0.4259987</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.0073669055</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-1.3324966</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.022687552</v>
-      </c>
-      <c r="DQ2" t="n">
+      <c r="DW2" t="n">
+        <v>0.17699814</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.0030610333</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.6107483</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.010420415</v>
+      </c>
+      <c r="EA2" t="n">
         <v>15</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="EB2" t="n">
         <v>15</v>
       </c>
-      <c r="DS2" t="b">
+      <c r="EC2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>CHINA MOTOR BUS</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="inlineStr">
         <is>
           <t>China Motor Bus Company, Limited</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>finmb_2482072</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EI2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EB2" t="b">
+      <c r="EK2" t="b">
         <v>0</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.43744528</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EG2" t="n">
-        <v>1782109003</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>946949400000</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>57.15 - 57.4</t>
-        </is>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
